--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488183_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488183_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6822</v>
+        <v>1.8426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.9617</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7927</v>
+        <v>0.8809</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5536</v>
+        <v>2.4371</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4339</v>
+        <v>1.0254</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1197</v>
+        <v>1.4117</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4217</v>
+        <v>2.5033</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7783</v>
+        <v>1.1762</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6434</v>
+        <v>1.3271</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8681</v>
+        <v>-0.0663</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3444</v>
+        <v>-0.1508</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4763</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.4087</v>
+        <v>0.9264</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0344</v>
+        <v>-0.2621</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1567</v>
+        <v>-0.6152</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8777</v>
+        <v>0.3531</v>
       </c>
       <c r="V2" t="n">
-        <v>0.503</v>
+        <v>-1.2589</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4403</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>Á. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4941</v>
+        <v>1.2441</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6132</v>
+        <v>1.2441</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8809</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4371</v>
+        <v>1.2441</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0254</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4117</v>
+        <v>1.2441</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5033</v>
+        <v>1.2441</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1762</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3271</v>
+        <v>1.2441</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0663</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1508</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08459999999999999</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6106</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9637</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3531</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Á. CHAPARRO CARRASCO</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2441</v>
+        <v>1.0017</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2441</v>
+        <v>0.3567</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2441</v>
+        <v>2.5536</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.4339</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2441</v>
+        <v>1.1197</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2441</v>
+        <v>4.4217</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3.7783</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2441</v>
+        <v>0.6434</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.8681</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.3444</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.4763</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.3761</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.7299</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4403</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1673</v>
+        <v>0.4129</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6181</v>
+        <v>1.716</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4508</v>
+        <v>-1.3031</v>
       </c>
       <c r="G5" t="n">
         <v>2.5997</v>
@@ -844,13 +844,13 @@
         <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8068</v>
+        <v>-0.5611</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4238</v>
+        <v>-0.2761</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0697</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.3186</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4157</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5032</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1646</v>
+        <v>0.45</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3058</v>
+        <v>-1.4885</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1413</v>
+        <v>1.9385</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3421</v>
+        <v>0.5167</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8291</v>
+        <v>-0.7689</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.487</v>
+        <v>1.2856</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1775</v>
+        <v>-0.0667</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5233</v>
+        <v>-0.7196</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3457</v>
+        <v>0.6529</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6956</v>
+        <v>-0.2431</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2014</v>
+        <v>-0.2207</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8971</v>
+        <v>-0.0224</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6992</v>
+        <v>-0.6294</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0692</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.043</v>
+        <v>-0.3236</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0271</v>
+        <v>0.5375</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9842</v>
+        <v>-0.8611</v>
       </c>
       <c r="G7" t="n">
         <v>-1.366</v>
@@ -1000,13 +1000,13 @@
         <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.3013</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3756</v>
+        <v>-0.1141</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2922</v>
+        <v>0.4153</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1536</v>
+        <v>-0.3262</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8811</v>
+        <v>-0.2631</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7275</v>
+        <v>-0.0631</v>
       </c>
       <c r="G8" t="n">
-        <v>0.45</v>
+        <v>0.1646</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4885</v>
+        <v>0.3058</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9385</v>
+        <v>-0.1413</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5167</v>
+        <v>1.3421</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7689</v>
+        <v>1.8291</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2856</v>
+        <v>-0.487</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0667</v>
+        <v>-1.1775</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7196</v>
+        <v>-1.5233</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6529</v>
+        <v>0.3457</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7153</v>
+        <v>0.282</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4713</v>
+        <v>-0.0488</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.244</v>
+        <v>0.3308</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6294</v>
+        <v>-1.6992</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6294</v>
+        <v>-1.0692</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1983</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2925</v>
+        <v>-2.8685</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0941</v>
+        <v>2.1926</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3884</v>
@@ -1156,13 +1156,13 @@
         <v>2.2234</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5967</v>
+        <v>0.1191</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1779</v>
+        <v>-0.3982</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4188</v>
+        <v>0.5173</v>
       </c>
       <c r="V9" t="n">
         <v>-0.63</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8087</v>
+        <v>-2.2889</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3987</v>
+        <v>-0.8544</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4099</v>
+        <v>-1.4346</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9578</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4628</v>
+        <v>0.0569</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9302</v>
+        <v>-0.3858</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4673</v>
+        <v>0.4427</v>
       </c>
       <c r="V10" t="n">
         <v>0.315</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0427</v>
+        <v>-2.6635</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6258</v>
+        <v>-2.3205</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4169</v>
+        <v>-0.343</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4695</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.856</v>
+        <v>-0.4769</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.549</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0018</v>
+        <v>0.0721</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0142</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5268</v>
+        <v>-7.0065</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0952</v>
+        <v>-6.6488</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4316</v>
+        <v>-0.3577</v>
       </c>
       <c r="G12" t="n">
         <v>-4.9845</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6372</v>
+        <v>-0.1169</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7113</v>
+        <v>-0.2649</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0741</v>
+        <v>0.148</v>
       </c>
       <c r="V12" t="n">
         <v>0.5034999999999999</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.011900000000001</v>
+        <v>-8.464699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.3169</v>
+        <v>-8.7698</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3050000000000002</v>
+        <v>0.3050000000000005</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7171</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.9059</v>
+        <v>-6.905899999999999</v>
       </c>
       <c r="I13" t="n">
         <v>2.188499999999999</v>
@@ -1468,10 +1468,10 @@
         <v>15.7494</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0942</v>
+        <v>-0.5470000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.805</v>
+        <v>-3.2579</v>
       </c>
       <c r="U13" t="n">
         <v>2.7107</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1537</v>
+        <v>6.4173</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3973</v>
+        <v>3.0056</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7564</v>
+        <v>3.4117</v>
       </c>
       <c r="G14" t="n">
         <v>0.0281</v>
@@ -1546,13 +1546,13 @@
         <v>1.8529</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4962</v>
+        <v>0.7598</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2114</v>
+        <v>-0.1803</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2848</v>
+        <v>0.9401</v>
       </c>
       <c r="V14" t="n">
         <v>3.7766</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6638</v>
+        <v>3.5709</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5071</v>
+        <v>1.1926</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1567</v>
+        <v>2.3783</v>
       </c>
       <c r="G15" t="n">
         <v>1.9159</v>
@@ -1624,13 +1624,13 @@
         <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0946</v>
+        <v>-0.1875</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2037</v>
+        <v>-0.5182</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1092</v>
+        <v>0.3308</v>
       </c>
       <c r="V15" t="n">
         <v>2.7689</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.72</v>
+        <v>1.3042</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.1419</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0884</v>
+        <v>1.1623</v>
       </c>
       <c r="G17" t="n">
         <v>0.2726</v>
@@ -1780,13 +1780,13 @@
         <v>0.9264</v>
       </c>
       <c r="S17" t="n">
-        <v>1.115</v>
+        <v>0.6992</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6491</v>
+        <v>0.1595</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4658</v>
+        <v>0.5397</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6997</v>
+        <v>1.1481</v>
       </c>
       <c r="E18" t="n">
-        <v>0.979</v>
+        <v>1.3707</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2793</v>
+        <v>-0.2226</v>
       </c>
       <c r="G18" t="n">
         <v>2.355</v>
@@ -1858,13 +1858,13 @@
         <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5927</v>
+        <v>-0.1443</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0396</v>
+        <v>-0.6479</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4469</v>
+        <v>0.5036</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6921</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5125</v>
+        <v>0.9626</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6251</v>
+        <v>0.723</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1125</v>
+        <v>0.2396</v>
       </c>
       <c r="G19" t="n">
         <v>0.0614</v>
@@ -1936,13 +1936,13 @@
         <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4753</v>
+        <v>-0.0252</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.424</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1869</v>
+        <v>0.222</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1007</v>
+        <v>-3.7247</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2877</v>
+        <v>3.9467</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0359</v>
+        <v>-0.5137</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4706</v>
+        <v>-1.6597</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5652</v>
+        <v>1.146</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6961</v>
+        <v>-1.6543</v>
       </c>
       <c r="K20" t="n">
-        <v>0.369</v>
+        <v>-1.7788</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3271</v>
+        <v>0.1244</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3397</v>
+        <v>1.1406</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1016</v>
+        <v>0.119</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2381</v>
+        <v>1.0216</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.7057</v>
+        <v>-1.297</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.6322</v>
+        <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2901</v>
+        <v>0.1439</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5209</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2308</v>
+        <v>0.6939</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5668</v>
+        <v>1.8888</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2523</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1027</v>
+        <v>-0.9315</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2144</v>
+        <v>-2.2759</v>
       </c>
       <c r="F21" t="n">
-        <v>4.1116</v>
+        <v>1.3444</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5137</v>
+        <v>2.0359</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6597</v>
+        <v>0.4706</v>
       </c>
       <c r="I21" t="n">
-        <v>1.146</v>
+        <v>1.5652</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6543</v>
+        <v>1.6961</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7788</v>
+        <v>0.369</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1244</v>
+        <v>1.3271</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1406</v>
+        <v>0.3397</v>
       </c>
       <c r="N21" t="n">
-        <v>0.119</v>
+        <v>0.1016</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0216</v>
+        <v>0.2381</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.297</v>
+        <v>-3.7057</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>-4.6322</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1808</v>
+        <v>0.1716</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0396</v>
+        <v>0.3457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8588</v>
+        <v>-0.1741</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8888</v>
+        <v>0.5668</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>0.2523</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2287</v>
+        <v>-1.1725</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5437</v>
+        <v>-1.4457</v>
       </c>
       <c r="F22" t="n">
-        <v>0.315</v>
+        <v>0.2732</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3662</v>
@@ -2170,13 +2170,13 @@
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1375</v>
+        <v>0.1937</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4924</v>
+        <v>-0.3945</v>
       </c>
       <c r="U22" t="n">
-        <v>0.63</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1763</v>
+        <v>-1.5865</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8884</v>
+        <v>-1.6925</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.288</v>
+        <v>0.106</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9762</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1751</v>
+        <v>0.4147</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4414</v>
+        <v>-0.2456</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2663</v>
+        <v>0.6603</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9515</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6052</v>
+        <v>-2.458</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1139</v>
+        <v>0.2118</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7191</v>
+        <v>-2.6698</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2838</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.426</v>
+        <v>-0.2789</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6365</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.012</v>
+        <v>9.664899999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3049000000000009</v>
+        <v>-0.3049000000000006</v>
       </c>
       <c r="F25" t="n">
-        <v>9.3169</v>
+        <v>9.969799999999999</v>
       </c>
       <c r="G25" t="n">
         <v>4.717299999999999</v>
@@ -2404,13 +2404,13 @@
         <v>12.97</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0943</v>
+        <v>1.747</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.7107</v>
+        <v>-2.7108</v>
       </c>
       <c r="U25" t="n">
-        <v>3.8052</v>
+        <v>4.458</v>
       </c>
       <c r="V25" t="n">
         <v>5.9799</v>
